--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=be0edce6497a574d</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SW Engineer - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, MLOps, MLflow, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer NEX</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Data Engineer - Remote</t>
+          <t>DevOps Engineer NEX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
+          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Azure Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Skilled Wound Care</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant - Remote</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,225 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sagent</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ImageTrend</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant Level</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ashapura Softech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SW Engineer - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, MLOps, MLflow, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, MLOps, MLflow, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer NEX</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Data Engineer - Remote</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>DevOps Engineer NEX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Azure Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2276,29 +2276,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>AI Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Skilled Wound Care</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,29 +2691,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant - Remote</t>
+          <t>IBP Demand Data Product Owner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Snowflake, Data Modeling, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
+          <t>https://www.indeed.com/viewjob?jk=091b1f8448a933e9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Software Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,15 +3321,260 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Data Modeling, Dimensional Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9008b1f3bfd772fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MS Fabric</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sagent</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ImageTrend</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance Data &amp; BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,38 +1427,38 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0edce6497a574d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ashapura Softech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ashapura Softech Pvt. Ltd.</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant Level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, MLOps, MLflow, CI/CD, Maven</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Azure Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,54 +1861,54 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer NEX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure Data Engineer - Remote</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>AI Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Skilled Wound Care</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,89 +2631,89 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IBP Demand Data Product Owner</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Snowflake, Data Modeling, Power BI, Git, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=091b1f8448a933e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant - Remote</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Heygen</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Equus Computer Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,295 +3286,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>mSupply</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Data Modeling, Dimensional Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9008b1f3bfd772fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Sagent</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Heygen</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Equus Computer Systems</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>City of Industry, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ImageTrend</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>STERIS</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Mentor, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1612776e805e54c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
+          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ashapura Softech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=0202017052eb87fc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ashapura Softech Pvt. Ltd.</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Data Engineer - Remote</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Azure Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>AI Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Skilled Wound Care</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WFP Senior Data Scientist</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Heygen</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Equus Computer Systems</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,85 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer Big Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=1275c892f53f1ddf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Solutions Advisor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>HiveMQ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9360489f9c29037f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashapura Softech Pvt. Ltd.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0202017052eb87fc</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Data Engineer - Remote</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e4e101c91d2cab</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WFP Senior Data Scientist</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>WFP Senior Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>Heygen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Equus Computer Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,15 +3356,50 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Software Engineer Big Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer Big Data</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1275c892f53f1ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Solutions Advisor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>HiveMQ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=9360489f9c29037f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solutions Advisor</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HiveMQ</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9360489f9c29037f</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,29 +1191,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>QICLink or QNXT Configuration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=51a905181c25aa42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>SW Engineer - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Skilled Wound Care</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,164 +2211,164 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9008b1f3bfd772fb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Solutions/Enterprise Architect (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5730ed2de660b62b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WFP Senior Data Scientist</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e3c168d86ea726</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Heygen</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,155 +3251,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>ImageTrend</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Azure data factory developer with Snowflake exp</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>STERIS</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Mentor, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Data Engineer, Finance Data &amp; BI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Solutions Advisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HiveMQ</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9360489f9c29037f</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,112 +1116,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QICLink or QNXT Configuration</t>
+          <t>AI Architect &amp; Workflow Operator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>We Invest Florida LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a905181c25aa42</t>
+          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant Level</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,137 +2001,137 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,42 +2176,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,435 +2831,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>mSupply</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Data Modeling, Dimensional Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9008b1f3bfd772fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Sr. Solutions/Enterprise Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Inspira Financial</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5730ed2de660b62b</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Sagent</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Heygen</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ImageTrend</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>STERIS</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Mentor, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba1f68994568fe5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Data Platform)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
+          <t>https://www.indeed.com/viewjob?jk=329a3eade67f9940</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Data Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=425ef1a26b020ab5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Data Architect (Data Platform)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=81f4767d72304e41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
+          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance Data &amp; BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,242 +881,242 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Architect &amp; Workflow Operator</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>We Invest Florida LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
@@ -1348,55 +1348,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer, Finance Data &amp; BI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Corebridge</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,49 +1406,49 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2e0b3c29bafcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,137 +1651,137 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=76153c3912d65896</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,207 +1791,207 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,207 +2141,207 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Architect &amp; Workflow Operator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>We Invest Florida LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=14f1c39aa588c7f7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=daa379deb564c9ec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,151 +2652,151 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,42 +2806,1897 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Tableau / Python Developer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CSpring</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>mSupply</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer (CEMI)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Wood Mackenzie</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GPS Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GPS Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Quality Systems Specialist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>North Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Total Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Data Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Snowflake Data Movement Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Site Reliability / Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>General Intuition &amp; Medal</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Governance Focus)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Arvest Bank</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Warehouse Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AGS - American Gaming Systems</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Duluth, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Altom Transport, Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83fcfc9537d38331</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Junior Cloud Security Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Java QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05d63312f544a52d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SPRING ARBOR UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Spring Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AAA Central Penn</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Seaside, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Stride, Inc.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Alvys</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MS Fabric</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sagent</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Azure data factory developer with Snowflake exp</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>IL, US USA</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D121" t="n">
         <v>10.4</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer (AWS, Airflow, DBT - Max $70/hr W2 )</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lenmar Consulting</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b55f02a558d6569b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba1f68994568fe5</t>
+          <t>https://www.indeed.com/viewjob?jk=27d1b768e1037d39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect (Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329a3eade67f9940</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba1f68994568fe5</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425ef1a26b020ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=329a3eade67f9940</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f4767d72304e41</t>
+          <t>https://www.indeed.com/viewjob?jk=425ef1a26b020ab5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Data Platform)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
+          <t>https://www.indeed.com/viewjob?jk=81f4767d72304e41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Cornerstone LMS Support Engineer (L2/L3)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c15b3244d5ea49</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance Data &amp; BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer, Finance Data &amp; BI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,15 +1493,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76153c3912d65896</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=76153c3912d65896</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Architect &amp; Workflow Operator</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>We Invest Florida LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>AI Architect &amp; Workflow Operator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>We Invest Florida LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f1c39aa588c7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa379deb564c9ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=14f1c39aa588c7f7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Tableau / Python Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
@@ -3233,52 +3233,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fcfc9537d38331</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
+          <t>https://www.indeed.com/viewjob?jk=df2f71bd1ac4fde2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d63312f544a52d</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,15 +3908,15 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=05d63312f544a52d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Solution Architect – GCP / GKE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+          <t>https://www.indeed.com/viewjob?jk=d097819844265040</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Software Engineer - AI Augmented Development</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PowerPay</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Quality Engineer (AWS, Airflow, DBT - Max $70/hr W2 )</t>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lenmar Consulting</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,15 +4686,85 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Azure data factory developer with Snowflake exp</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer (AWS, Airflow, DBT - Max $70/hr W2 )</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Lenmar Consulting</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>AWS, Glue, Redshift, RDS, Spark, PySpark, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b55f02a558d6569b</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cornerstone LMS Support Engineer (L2/L3)</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c15b3244d5ea49</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Cornerstone LMS Support Engineer (L2/L3)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c15b3244d5ea49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,137 +1336,137 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance Data &amp; BI</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
+          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,15 +1493,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76153c3912d65896</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Devops Engineer SR</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Architect &amp; Workflow Operator</t>
+          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>We Invest Florida LLC</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
+          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+          <t>AI Architect &amp; Workflow Operator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>We Invest Florida LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior Information Systems Analyst - Cloud Specialization</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heluna Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Alhambra, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, BigQuery, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1b66aae8e310f7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f1c39aa588c7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tableau / Python Developer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Analytics Engineer (Tableau / Python)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Information Management Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c459753bd1cdb02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9f31acafb196f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
+          <t>https://www.indeed.com/viewjob?jk=eddf440d2f5e6a08</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b90c44b778c96e5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02cbd4d4f3ab1a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=c72708184be593b0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0183a968afa2cc49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=396d9bc5ea519b3f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecd68d84aeeeb2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2f498b47a3dade5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb725340d17f5f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2f71bd1ac4fde2</t>
+          <t>https://www.indeed.com/viewjob?jk=6157c3d64ba51e2f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
+          <t>https://www.indeed.com/viewjob?jk=520e85bbd545fd30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=786d87c02c6e82fb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0c7773db64eb1d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
+          <t>https://www.indeed.com/viewjob?jk=55e84c3eece43f91</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0ea4078cfef29b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=334a63469248ffd9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ab02a6d7de0e22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=5de616281a6596e7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=263c1568fbef1b4e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d63312f544a52d</t>
+          <t>https://www.indeed.com/viewjob?jk=a927ea91cbb8a50f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6383bd749b920c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f56fb77c91d02050</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c96e34675c53889</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=df1068f91cfbd0ea</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,137 +4101,137 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=809020eea7aab65e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=0606d3d67bc3282b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=73db59dcad1e76b8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alvys</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=95a144418b5a39ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Solution Architect – GCP / GKE</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d097819844265040</t>
+          <t>https://www.indeed.com/viewjob?jk=4a02f9792dbc45ec</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
+          <t>https://www.indeed.com/viewjob?jk=917d4d97f814ea4e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec1b251622a39c3d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
+          <t>https://www.indeed.com/viewjob?jk=5a08aa2cdbe9c831</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=f764f8b0e7d0312f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=2db3e1701039a3d8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e71b02a56bd9a3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,242 +4486,242 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=06a90bd586bd83f5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea90c167478f7b2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e665c6e81af078e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=407f8be7ec057cfd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=94c251dd631ae9fd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer SR - Full Stack .NET/React</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
+          <t>https://www.indeed.com/viewjob?jk=04ee9ae955c7787c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1d976cf3a8a264f5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,40 +4731,2035 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a7ba28491bf8d5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5adb7e6fb7d93b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=728bdd335b56b5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de36d6aa4de5c8d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Full Stack Development Intern</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a00102caa3003ef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Wood Mackenzie</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Total Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Data Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Snowflake Data Movement Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Site Reliability / Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>General Intuition &amp; Medal</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Governance Focus)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Warehouse Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>AGS - American Gaming Systems</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Duluth, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Al Warren Oil Company, Inc.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bensenville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af471adc52c88153</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Al Warren Oil Company, Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=916ff0070c873866</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Junior Cloud Security Analyst</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>QA Analyst / ETL Tester</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CSpring</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Candescent (Digital First Holdings LLC)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05c875eff000793f</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior eCommerce Microservices Developer - Onsite</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Bass Pro Shops</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e26470cca0ea4331</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SPRING ARBOR UNIVERSITY</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Spring Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AAA Central Penn</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BigData ,Python and Py Spark , GCP</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Seaside, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Stride, Inc.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Engineer, Senior</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b86ad107b3f52c</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Solution Architect – GCP / GKE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>THEMESOFT</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d097819844265040</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Azure data factory developer with Snowflake exp</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54abe916af0096bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddefa346a4deb1f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>Data Quality Engineer (AWS, Airflow, DBT - Max $70/hr W2 )</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Lenmar Consulting</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Reston, VA, US USA</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D181" t="n">
         <v>10.4</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>AWS, Glue, Redshift, RDS, Spark, PySpark, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b55f02a558d6569b</t>
         </is>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect (Data Platform)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Skyventure Management LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, S3, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329a3eade67f9940</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf4e196f6f8959b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect (Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425ef1a26b020ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect (Data Platform)</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f4767d72304e41</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6284fe79cf0d13</t>
+          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Data Engineer &amp; Database Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f3235028b4cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cornerstone LMS Support Engineer (L2/L3)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c15b3244d5ea49</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer with ML</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9776c14731d7381</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,15 +2018,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Operations (MLOps) Architect - Generative Al Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Databricks, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73469e8d3cab7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=6407c9a76bdb537c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Architect &amp; Workflow Operator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>We Invest Florida LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6822c6de2c9090a</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Information Systems Analyst - Cloud Specialization</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alhambra, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, BigQuery, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,42 +2351,42 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1b66aae8e310f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbff1064107d9a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Analytics Engineer (Tableau / Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer (CEMI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Tableau / Python)</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,15 +3138,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Information Management Data Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c459753bd1cdb02</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9f31acafb196f</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eddf440d2f5e6a08</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b90c44b778c96e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02cbd4d4f3ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Data Engineer (Governance Focus)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72708184be593b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0183a968afa2cc49</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396d9bc5ea519b3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecd68d84aeeeb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f498b47a3dade5</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb725340d17f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6157c3d64ba51e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520e85bbd545fd30</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786d87c02c6e82fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>BigData ,Python and Py Spark , GCP</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0c7773db64eb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e84c3eece43f91</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0ea4078cfef29b</t>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334a63469248ffd9</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ab02a6d7de0e22</t>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de616281a6596e7</t>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=263c1568fbef1b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Software Engineer - AI Augmented Development</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>PowerPay</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a927ea91cbb8a50f</t>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6383bd749b920c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,172 +3996,172 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56fb77c91d02050</t>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c96e34675c53889</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1068f91cfbd0ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809020eea7aab65e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0606d3d67bc3282b</t>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Azure data factory developer with Snowflake exp</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73db59dcad1e76b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,2562 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a144418b5a39ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a02f9792dbc45ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=917d4d97f814ea4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>New Franken, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec1b251622a39c3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Kansas City, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a08aa2cdbe9c831</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f764f8b0e7d0312f</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Okemos, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2db3e1701039a3d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Charleston, WV, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e71b02a56bd9a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Upper Darby, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06a90bd586bd83f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea90c167478f7b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e665c6e81af078e</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Columbia, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=407f8be7ec057cfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94c251dd631ae9fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ee9ae955c7787c</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d976cf3a8a264f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a7ba28491bf8d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5adb7e6fb7d93b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=728bdd335b56b5a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Remote</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de36d6aa4de5c8d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Full Stack Development Intern</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Leidos</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a00102caa3003ef3</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AI Systems Administrator</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>AI Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Wood Mackenzie</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Total Wine &amp; More</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>PitchBook</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Junior GCP Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer / Data Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Snowflake Data Movement Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Smart Tech Skills LLC</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>General Intuition &amp; Medal</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Data Warehouse Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>AGS - American Gaming Systems</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Duluth, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, PostgreSQL, DynamoDB, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604b4cf6d66c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Al Warren Oil Company, Inc.</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Bensenville, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af471adc52c88153</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Al Warren Oil Company, Inc.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=916ff0070c873866</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1d220b240e828a</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior GCP IAM Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Junior Cloud Security Analyst</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e6c20b5ea1eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddad85975e3eaad7</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>QA Analyst / ETL Tester</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>CSpring</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Candescent (Digital First Holdings LLC)</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05c875eff000793f</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior eCommerce Microservices Developer - Onsite</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Bass Pro Shops</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26470cca0ea4331</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Spring Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior GCP Kubernetes Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>AAA Central Penn</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Leidos</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Seaside, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Data Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Stride, Inc.</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Data Engineering &amp; Operations Specialist</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Shelter Insurance</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b86ad107b3f52c</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior Solution Architect – GCP / GKE</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>THEMESOFT</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d097819844265040</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Software Engineer - AI Augmented Development</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>PowerPay</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Wayne, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Google Cloud Platform, Vertex AI, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc0ff5761592934</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Azure data factory developer with Snowflake exp</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior GCP Kubernetes Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, Splunk, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a67e047e2a2075b</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54abe916af0096bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Imprint</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, DynamoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddefa346a4deb1f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS, Airflow, DBT - Max $70/hr W2 )</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Lenmar Consulting</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f02a558d6569b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-05.xlsx
+++ b/results/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
@@ -818,35 +818,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Java Developer – R01564833</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, Azure, GCP, HBase, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,15 +2018,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6407c9a76bdb537c</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e21e28ac2d2e959</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,49 +2596,49 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Tableau / Python)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer (Tableau / Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (CEMI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e495805b383735ac</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,104 +3076,104 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4add320b3e21c2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AGS - American Gaming Systems</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3702,11 +3702,11 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AGS - American Gaming Systems</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>RDS, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8b285f6f23691</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,59 +3961,59 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=40cace09139f1b6b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>BigData ,Python and Py Spark , GCP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,15 +4196,505 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Seaside, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Engineer II-Software Development</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Engineer II-Software Development</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Test Automation Architect (Data Migration &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Atlantis IT Group</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Scala, Snowflake, Oracle, SQL Server, ETL, ELT, CI/CD, pytest, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=706847de763fb7d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f5a7a92a5f943c</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379785b95cc4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Azure data factory developer with Snowflake exp</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>
